--- a/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11964</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57161</t>
+          <t>57754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83284</t>
+          <t>84283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101371</t>
+          <t>101687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>44223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>71294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88455</t>
+          <t>88151</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111903</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153908</t>
+          <t>153660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>180210</t>
+          <t>179765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>404</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>462</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>909</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>66002</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>91424</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>54553</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>126292</t>
+          <t>127103</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>158401</t>
+          <t>159926</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>854</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>782</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>76560</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>62433</t>
+          <t>62735</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>77213</t>
+          <t>77019</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>131195</t>
+          <t>132366</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>150898</t>
+          <t>151428</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>52138</t>
+          <t>51265</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>27754</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>48959</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>33605</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>63226</t>
+          <t>60677</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>66814</t>
+          <t>66152</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>100004</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>275054</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519201</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>570088</t>
+          <t>569331</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1172,82 +1172,82 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1398,72 +1398,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3854</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9976</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5384</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1511,72 +1511,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>326</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>326</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1624,72 +1624,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13156</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8363</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4842</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13199</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8798</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13297</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49090</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41513</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55763</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41903</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36589</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45964</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51361</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57754</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>91356</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84283</t>
+          <t>82285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>99615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,47 +2080,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2193,82 +2193,82 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>569</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2419,82 +2419,82 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>323</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2532,82 +2532,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5279</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2758,72 +2758,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5633</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9030</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2871,47 +2871,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>358</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>7167</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12011</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>17268</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11232</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>32889</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>26,1%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>10374</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>6204</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>16215</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>28965</t>
+          <t>27513</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>19676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44223</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>96518</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>83020</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>103942</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>65219</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>57646</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>71294</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>74,29%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>65,67%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>81,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>103469</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88151</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111859</t>
+          <t>71528</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>168688</t>
+          <t>161203</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153660</t>
+          <t>147782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>179765</t>
+          <t>172316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>86748</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>86748</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>86748</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>135607</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>135607</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>135607</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>326</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3440,47 +3440,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1138</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3553,47 +3553,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5737</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4005,72 +4005,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>6445</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>5778</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>7595</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>799</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4231,72 +4231,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>7495</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>4516</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>7887</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>14041</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>6204</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>13058</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>13,07%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>14352</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>54545</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>46759</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>61580</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>67,95%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>58,25%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>76,72%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>78201</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>66002</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>91424</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>49240</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>53666</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>93304</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>159926</t>
+          <t>113623</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>71566</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>71566</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>71566</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>89372</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,82 +4800,82 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>5799</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>4463</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4913,82 +4913,82 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>3969</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>4377</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>891</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -5026,82 +5026,82 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>777</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5478,47 +5478,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>4308</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>825</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>4042</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5704,47 +5704,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>3952</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>8589</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>14144</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>12913</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>8468</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>19597</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>66457</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>59764</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>72345</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>79,56%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>71,55%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>71354</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>64517</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>77109</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>62735</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>74330</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>132366</t>
+          <t>125187</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>151428</t>
+          <t>143543</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>89650</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>89650</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>89650</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>243</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6160,72 +6160,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,22 +6235,22 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -6273,72 +6273,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>5978</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,22 +6348,22 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6386,82 +6386,82 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6549,49 +6549,49 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -6612,72 +6612,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6725,72 +6725,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>8622</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>7611</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>9063</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6838,72 +6838,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>17711</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>8069</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>15478</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6951,72 +6951,72 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>9161</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>8930</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7064,72 +7064,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>29605</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>10164</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>23670</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>51265</t>
+          <t>47878</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -7177,72 +7177,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>42107</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>32148</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>59117</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>38289</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>27754</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>49269</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>39583</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>60677</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>66152</t>
+          <t>68681</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>100004</t>
+          <t>99951</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>256677</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>242664</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>275054</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>519201</t>
+          <t>469918</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>569331</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>979</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
